--- a/sample-data/Payroll_aggregate_2026-05.xlsx
+++ b/sample-data/Payroll_aggregate_2026-05.xlsx
@@ -451,7 +451,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -480,7 +480,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>0</v>
       </c>
       <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
         <v>1</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -596,7 +596,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -654,7 +654,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9">
         <v>0</v>

--- a/sample-data/Payroll_aggregate_2026-05.xlsx
+++ b/sample-data/Payroll_aggregate_2026-05.xlsx
@@ -436,7 +436,7 @@
         <v>Technology</v>
       </c>
       <c r="C2" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D2">
         <v>31</v>
@@ -465,7 +465,7 @@
         <v>Sales</v>
       </c>
       <c r="C3" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D3">
         <v>26</v>
@@ -494,7 +494,7 @@
         <v>Operations</v>
       </c>
       <c r="C4" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D4">
         <v>23</v>
@@ -523,7 +523,7 @@
         <v>Customer Support</v>
       </c>
       <c r="C5" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D5">
         <v>16</v>
@@ -552,7 +552,7 @@
         <v>Finance</v>
       </c>
       <c r="C6" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D6">
         <v>12</v>
@@ -581,7 +581,7 @@
         <v>Human Resources</v>
       </c>
       <c r="C7" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D7">
         <v>8</v>
@@ -610,7 +610,7 @@
         <v>Product</v>
       </c>
       <c r="C8" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D8">
         <v>11</v>
@@ -639,7 +639,7 @@
         <v>Marketing</v>
       </c>
       <c r="C9" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D9">
         <v>8</v>
